--- a/Sajjad data/by_country_and_state/USA/UT.xlsx
+++ b/Sajjad data/by_country_and_state/USA/UT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="464">
   <si>
     <t>Business Name</t>
   </si>
@@ -173,6 +173,1236 @@
   </si>
   <si>
     <t>2026-10-24T19:45:48.590Z</t>
+  </si>
+  <si>
+    <t>Stephens Emergency Dentist</t>
+  </si>
+  <si>
+    <t>(801) 597-4417</t>
+  </si>
+  <si>
+    <t>Emergency dental service</t>
+  </si>
+  <si>
+    <t>2225 E Murray Holladay Rd #109, Holladay, UT 84117</t>
+  </si>
+  <si>
+    <t>Holladay</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stephens+Emergency+Dentist/data=!4m7!3m6!1s0x87526227768b814b:0xb1ba3f1497b8ca7b!8m2!3d40.6678451!4d-111.8272755!16s%2Fg%2F1tflshg1!19sChIJS4GLdidiUocRe8q4lxQ_urE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:24.145Z</t>
+  </si>
+  <si>
+    <t>Connolly Family Dental</t>
+  </si>
+  <si>
+    <t>(801) 467-4747</t>
+  </si>
+  <si>
+    <t>1963 E 2700 S, Salt Lake City, UT 84106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Connolly+Family+Dental/data=!4m7!3m6!1s0x875260364edca94d:0xf5c6565b19353b34!8m2!3d40.712983!4d-111.8349876!16s%2Fg%2F1tg4x9vq!19sChIJTancTjZgUocRNDs1GVtWxvU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:11.892Z</t>
+  </si>
+  <si>
+    <t>Dr. Jonathan C. Liddell, DMD</t>
+  </si>
+  <si>
+    <t>(801) 359-8282</t>
+  </si>
+  <si>
+    <t>702 E S Temple St #209, Salt Lake City, UT 84102</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jonathan+C.+Liddell,+DMD/data=!4m7!3m6!1s0x8752f57067cb522f:0x774e613c290cd614!8m2!3d40.7689773!4d-111.8705454!16s%2Fg%2F1tfp2ygg!19sChIJL1LLZ3D1UocRFNYMKTxhTnc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:17.004Z</t>
+  </si>
+  <si>
+    <t>ProCare Dental</t>
+  </si>
+  <si>
+    <t>(801) 278-2817</t>
+  </si>
+  <si>
+    <t>1377 E 3900 S #202, Salt Lake City, UT 84124</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ProCare+Dental/data=!4m7!3m6!1s0x875261dec4769647:0xed3eabc7f6d69cf0!8m2!3d40.6872757!4d-111.8521842!16s%2Fg%2F1thxr3c_!19sChIJR5Z2xN5hUocR8JzW9serPu0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:14.514Z</t>
+  </si>
+  <si>
+    <t>Rose Park Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(801) 519-2222</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>55 N Redwood Rd Suite B, Salt Lake City, UT 84116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rose+Park+Pediatric+Dentistry/data=!4m7!3m6!1s0x8752f47acb628acf:0x17a3c00ce0f9d88b!8m2!3d40.7706389!4d-111.9399858!16s%2Fg%2F1tjwj6zf!19sChIJz4piy3r0UocRi9j54AzAoxc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:30.726Z</t>
+  </si>
+  <si>
+    <t>Dr. Jeffery K. Rupp DMD, MS</t>
+  </si>
+  <si>
+    <t>(801) 463-1900</t>
+  </si>
+  <si>
+    <t>1548 E 4500 S STE 102, Salt Lake City, UT 84117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jeffery+K.+Rupp+DMD,+MS/data=!4m7!3m6!1s0x8752601c34ea18bb:0x54ec60de3dff53a5!8m2!3d40.6740149!4d-111.8454307!16s%2Fg%2F1hm50k2y0!19sChIJuxjqNBxgUocRpVP_Pd5g7FQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:33.574Z</t>
+  </si>
+  <si>
+    <t>A Kid's Place Dentistry</t>
+  </si>
+  <si>
+    <t>(801) 747-8000</t>
+  </si>
+  <si>
+    <t>530 500 S, Salt Lake City, UT 84102</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/A+Kid%27s+Place+Dentistry/data=!4m7!3m6!1s0x8752f56a309e2a9d:0xe1242f333c3ea545!8m2!3d40.7595651!4d-111.8759699!16s%2Fg%2F1tplqt4m!19sChIJnSqeMGr1UocRRaU-PDMvJOE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:36.398Z</t>
+  </si>
+  <si>
+    <t>Cottonwood Pediatric Dental</t>
+  </si>
+  <si>
+    <t>(801) 943-3233</t>
+  </si>
+  <si>
+    <t>7050 S Highland Dr, Cottonwood Heights, UT 84121</t>
+  </si>
+  <si>
+    <t>Cottonwood Heights</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cottonwood+Pediatric+Dental/data=!4m7!3m6!1s0x87526269a98e8d57:0xa371f93e80d33f19!8m2!3d40.6229962!4d-111.8346588!16s%2Fg%2F1wb8v53q!19sChIJV42OqWliUocRGT_TgD75caM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:41.742Z</t>
+  </si>
+  <si>
+    <t>Aloha Pediatric Dental-Orthdntcs: Mandelaris Jason G DDS</t>
+  </si>
+  <si>
+    <t>(801) 969-9669</t>
+  </si>
+  <si>
+    <t>2792 S 5600 W, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aloha+Pediatric+Dental-Orthdntcs:+Mandelaris+Jason+G+DDS/data=!4m7!3m6!1s0x8752f2b57406ab81:0x5fd1d3b696769008!8m2!3d40.7092857!4d-112.025536!16s%2Fg%2F113gm8dsl!19sChIJgasGdLXyUocRCJB2lrbT0V8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:45.568Z</t>
+  </si>
+  <si>
+    <t>Jeffrey Chandler</t>
+  </si>
+  <si>
+    <t>(801) 581-1234</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>1400 S Foothill Dr #240, Salt Lake City, UT 841082327</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jeffrey+Chandler/data=!4m7!3m6!1s0x87526071862fffff:0x41b9e5eabe88354c!8m2!3d40.7386592!4d-111.8268157!16s%2Fg%2F11rkj7vrhz!19sChIJ__8vhnFgUocRTDWIvurluUE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:01.653Z</t>
+  </si>
+  <si>
+    <t>Dr. Jonathan Reed Emergency Dentist West Jordan 24 Hours</t>
+  </si>
+  <si>
+    <t>(385) 403-8900</t>
+  </si>
+  <si>
+    <t>7709 1700 W, West Jordan, UT 84084</t>
+  </si>
+  <si>
+    <t>West Jordan</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jonathan+Reed+Emergency+Dentist+West+Jordan+24+Hours/data=!4m7!3m6!1s0x8752894314501dbf:0xeed7920a579b8ae3!8m2!3d40.6107878!4d-111.9384972!16s%2Fg%2F11zx14d78q!19sChIJvx1QFEOJUocR44qbVwqS1-4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:32.851Z</t>
+  </si>
+  <si>
+    <t>Urgent Dentist Access</t>
+  </si>
+  <si>
+    <t>(801) 515-0162</t>
+  </si>
+  <si>
+    <t>220 N 2200 W ste 100, Salt Lake City, UT 84116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dentist+Access/data=!4m7!3m6!1s0x8752f5799cab525b:0xf631f63e5dd9131a!8m2!3d40.7734019!4d-111.9519485!16s%2Fg%2F11p2259y_5!19sChIJW1KrnHn1UocRGhPZXT72MfY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:35.779Z</t>
+  </si>
+  <si>
+    <t>Dr. Barry Barrett Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(385) 247-8808</t>
+  </si>
+  <si>
+    <t>253 UT-71, Draper, UT 84020</t>
+  </si>
+  <si>
+    <t>Draper</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Barry+Barrett+Emergency+Dental+Service/data=!4m7!3m6!1s0x875287c3d091d82b:0x89c6b1daea0a7365!8m2!3d40.527072!4d-111.883635!16s%2Fg%2F11zd329l4l!19sChIJK9iR0MOHUocRZXMK6tqxxok?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:39.046Z</t>
+  </si>
+  <si>
+    <t>Smilora Teeth Whitening &amp; Spa</t>
+  </si>
+  <si>
+    <t>(801) 814-7838</t>
+  </si>
+  <si>
+    <t>Beauty salon</t>
+  </si>
+  <si>
+    <t>6679 W 7870 S, West Jordan, UT 84081</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smilora+Teeth+Whitening+%26+Spa/data=!4m7!3m6!1s0x8752916fe72fd477:0x2d1a37ce15bb529a!8m2!3d40.6079998!4d-112.0500822!16s%2Fg%2F11y0ss61cc!19sChIJd9Qv52-RUocRmlK7Fc43Gi0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:07.478Z</t>
+  </si>
+  <si>
+    <t>South Valley Periodontics</t>
+  </si>
+  <si>
+    <t>(801) 572-0333</t>
+  </si>
+  <si>
+    <t>8938 S State St, Sandy, UT 84070</t>
+  </si>
+  <si>
+    <t>Sandy</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Valley+Periodontics/data=!4m7!3m6!1s0x8752886fe66a9eff:0x89949240a7740d22!8m2!3d40.5890832!4d-111.8923345!16s%2Fg%2F1tgwbcy4!19sChIJ_55q5m-IUocRIg10p0CSlIk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:47.964Z</t>
+  </si>
+  <si>
+    <t>Steven M Canfield DDS</t>
+  </si>
+  <si>
+    <t>(801) 261-3635</t>
+  </si>
+  <si>
+    <t>4970 S 900 E Ste D, Salt Lake City, UT 84117</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Steven+M+Canfield+DDS/data=!4m7!3m6!1s0x87528a026eafa1f5:0x2a321e58e590a479!8m2!3d40.6615041!4d-111.8659168!16s%2Fg%2F1td8zlvf!19sChIJ9aGvbgKKUocReaSQ5VgeMio?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:52.977Z</t>
+  </si>
+  <si>
+    <t>Alan Aoki PC</t>
+  </si>
+  <si>
+    <t>(801) 322-4600</t>
+  </si>
+  <si>
+    <t>702 E S Temple St #105, Salt Lake City, UT 84102</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alan+Aoki+PC/data=!4m7!3m6!1s0x8752f57067cb522f:0xf6202d9a5cc749de!8m2!3d40.7689992!4d-111.8704823!16s%2Fg%2F1vzv445f!19sChIJL1LLZ3D1UocR3knHXJotIPY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:55.541Z</t>
+  </si>
+  <si>
+    <t>Dr. Scot D. Drury, DDS</t>
+  </si>
+  <si>
+    <t>(801) 582-9351</t>
+  </si>
+  <si>
+    <t>3018 E 3300 S, Salt Lake City, UT 84109</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Scot+D.+Drury,+DDS/data=!4m7!3m6!1s0x87526071a07a588b:0xc280ca4e2877984!8m2!3d40.699577!4d-111.8074436!16s%2Fg%2F1wzt2vw1!19sChIJi1h6oHFgUocRhHmH4qQMKAw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:58.909Z</t>
+  </si>
+  <si>
+    <t>Mountain View Dental</t>
+  </si>
+  <si>
+    <t>(801) 432-7773</t>
+  </si>
+  <si>
+    <t>Doctor</t>
+  </si>
+  <si>
+    <t>2854 W 4700 S suite b, West Valley City, UT 84119</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mountain+View+Dental/data=!4m7!3m6!1s0x87528c710e4de083:0x32e6b5af612c858f!8m2!3d40.6683702!4d-111.9605608!16s%2Fg%2F11dfgszmck!19sChIJg-BNDnGMUocRj4UsYa-15jI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:15.118Z</t>
+  </si>
+  <si>
+    <t>Orthodontics Dentist</t>
+  </si>
+  <si>
+    <t>(801) 304-9391</t>
+  </si>
+  <si>
+    <t>S Center St, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Orthodontics+Dentist/data=!4m7!3m6!1s0x87528a2364d48c13:0x1d77d87ab34af848!8m2!3d40.665209!4d-111.886128!16s%2Fg%2F1hm2q_lg7!19sChIJE4zUZCOKUocRSPhKs3rYdx0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:20.363Z</t>
+  </si>
+  <si>
+    <t>Dr. Christopher DeMille, DDS</t>
+  </si>
+  <si>
+    <t>(801) 969-3025</t>
+  </si>
+  <si>
+    <t>3454 S 4800 W, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Christopher+DeMille,+DDS/data=!4m7!3m6!1s0x87528d215f290ce3:0xfb716492b964613!8m2!3d40.6974211!4d-112.0060945!16s%2Fg%2F1tfmcqhb!19sChIJ4wwpXyGNUocRE0aWK0kWtw8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:23.128Z</t>
+  </si>
+  <si>
+    <t>Harmon Building</t>
+  </si>
+  <si>
+    <t>(801) 969-8261</t>
+  </si>
+  <si>
+    <t>Business center</t>
+  </si>
+  <si>
+    <t>3540 S 4000 W, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>1050</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Harmon+Building/data=!4m7!3m6!1s0x87528cc2b7c56d23:0xce7e9af06e3000d1!8m2!3d40.6963041!4d-111.987369!16s%2Fg%2F11fnqvwkz4!19sChIJI23Ft8KMUocR0QAwbvCafs4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:25.695Z</t>
+  </si>
+  <si>
+    <t>Egan Kelly C DDS</t>
+  </si>
+  <si>
+    <t>(801) 968-0798</t>
+  </si>
+  <si>
+    <t>4445 W 3500 S, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Egan+Kelly+C+DDS/data=!4m7!3m6!1s0x87528c82bdb3e94f:0x6ce3c109b26cccc4!8m2!3d40.696385!4d-111.997021!16s%2Fg%2F1jgm3vmjm!19sChIJT-mzvYKMUocRxMxssgnB42w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:24:41.707Z</t>
+  </si>
+  <si>
+    <t>Odontologia</t>
+  </si>
+  <si>
+    <t>(801) 969-8881</t>
+  </si>
+  <si>
+    <t>3725 W 4100 S, West Valley City, UT 84120</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Odontologia/data=!4m7!3m6!1s0x87528decb57ce831:0x72c7ce8677524fa8!8m2!3d40.6813718!4d-111.9801415!16s%2Fg%2F11ghshp52t!19sChIJMeh8teyNUocRqE9Sd4bOx3I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:44.130Z</t>
+  </si>
+  <si>
+    <t>Jordan West Dr- Utah Dentist.</t>
+  </si>
+  <si>
+    <t>(833) 844-0928</t>
+  </si>
+  <si>
+    <t>9269 S Redwood Rd, West Jordan, UT 84088</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jordan+West+Dr-+Utah+Dentist./data=!4m7!3m6!1s0x875288ba388c05cf:0xb0fc0439e6a5d796!8m2!3d40.5828679!4d-111.9383426!16s%2Fg%2F1tfwqfxp!19sChIJzwWMOLqIUocRltel5jkE_LA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:27:05.865Z</t>
+  </si>
+  <si>
+    <t>Provo Dental Assisting School</t>
+  </si>
+  <si>
+    <t>(801) 377-6453</t>
+  </si>
+  <si>
+    <t>Dental school</t>
+  </si>
+  <si>
+    <t>1355 N University Ave #330, Provo, UT 84604</t>
+  </si>
+  <si>
+    <t>Provo</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Provo+Dental+Assisting+School/data=!4m7!3m6!1s0x874d90a3dab9b12d:0x39e9a34b128c40d3!8m2!3d40.2524375!4d-111.6592514!16s%2Fg%2F1thvyrtd!19sChIJLbG52qOQTYcR00CMEkuj6Tk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:30:08.161Z</t>
+  </si>
+  <si>
+    <t>Gary M Hulet, DMD</t>
+  </si>
+  <si>
+    <t>(801) 375-1275</t>
+  </si>
+  <si>
+    <t>777 N 500 W Ste 101B, Provo, UT 84601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gary+M+Hulet,+DMD/data=!4m7!3m6!1s0x874d9a0875c5f30f:0xd7aaeda6f6b7b65b!8m2!3d40.2438105!4d-111.6678583!16s%2Fg%2F1tvym7kr!19sChIJD_PFdQiaTYcRW7a39qbtqtc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:03.244Z</t>
+  </si>
+  <si>
+    <t>Smile Center, Dr. Robert Jones, DDS</t>
+  </si>
+  <si>
+    <t>(801) 375-8770</t>
+  </si>
+  <si>
+    <t>10 S 300 E, Provo, UT 84606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smile+Center,+Dr.+Robert+Jones,+DDS/data=!4m7!3m6!1s0x874d9751154a64bf:0x71da0b7a84083f8c!8m2!3d40.2333967!4d-111.653727!16s%2Fg%2F1tg1668n!19sChIJv2RKFVGXTYcRjD8IhHoL2nE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:43.987Z</t>
+  </si>
+  <si>
+    <t>Millennial Dental</t>
+  </si>
+  <si>
+    <t>(801) 960-3644</t>
+  </si>
+  <si>
+    <t>3651 100 E, Provo, UT 84604</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Millennial+Dental/data=!4m7!3m6!1s0x874d907b086c5d15:0xc3fe450528e0a7d1!8m2!3d40.2818467!4d-111.6570946!16s%2Fg%2F11bv3trt59!19sChIJFV1sCHuQTYcR0afgKAVF_sM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:47.950Z</t>
+  </si>
+  <si>
+    <t>Dr. Nathan Hanson</t>
+  </si>
+  <si>
+    <t>(801) 356-1211</t>
+  </si>
+  <si>
+    <t>3685 100 E #B, Provo, UT 84604</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Nathan+Hanson/data=!4m7!3m6!1s0x874d907aff80a5fb:0xca319ba8628ea610!8m2!3d40.2825224!4d-111.6571277!16s%2Fg%2F11qgb76nhw!19sChIJ-6WA_3qQTYcREKaOYqibMco?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:43.339Z</t>
+  </si>
+  <si>
+    <t>White Wave Whitening</t>
+  </si>
+  <si>
+    <t>(435) 608-1395</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>3707 N Canyon Rd Ste 8F, Provo, UT 84604</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/White+Wave+Whitening/data=!4m7!3m6!1s0x874d9158ed4d3665:0x82e164eac590b5b8!8m2!3d40.2829466!4d-111.652518!16s%2Fg%2F11vwrj4v6j!19sChIJZTZN7ViRTYcRuLWQxepk4YI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:38.963Z</t>
+  </si>
+  <si>
+    <t>Utah Dentists</t>
+  </si>
+  <si>
+    <t>(801) 254-1471</t>
+  </si>
+  <si>
+    <t>10393 S 1300 W, South Jordan, UT 84095</t>
+  </si>
+  <si>
+    <t>South Jordan</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Utah+Dentists/data=!4m7!3m6!1s0x87528622a793d49b:0x77b8273714d2066e!8m2!3d40.562484!4d-111.928343!16s%2Fg%2F11c0ql8cq7!19sChIJm9STpyKGUocRbgbSFDcnuHc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:24.165Z</t>
+  </si>
+  <si>
+    <t>James D Johnson DDS PC</t>
+  </si>
+  <si>
+    <t>(801) 423-5519</t>
+  </si>
+  <si>
+    <t>2651 10400 S, South Jordan, UT 84095</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+D+Johnson+DDS+PC/data=!4m7!3m6!1s0x875285fec05718f7:0x2984fad8a2ca1e86!8m2!3d40.5619264!4d-111.9564326!16s%2Fg%2F1tdb99hw!19sChIJ9xhXwP6FUocRhh7Kotj6hCk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:47.774Z</t>
+  </si>
+  <si>
+    <t>Osborne Dental South Jordan</t>
+  </si>
+  <si>
+    <t>(801) 255-7243</t>
+  </si>
+  <si>
+    <t>3674 S Jordan Pkwy W #102, South Jordan, UT 84009</t>
+  </si>
+  <si>
+    <t>Closed · Opens 8 AM Mon · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Osborne+Dental+South+Jordan/data=!4m7!3m6!1s0x875288b7dd3ffaef:0x8587ad925b492134!8m2!3d40.563402!4d-111.978636!16s%2Fg%2F1hc1n6z2w!19sChIJ7_o_3beIUocRNCFJW5Kth4U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:50.593Z</t>
+  </si>
+  <si>
+    <t>Almond Dental</t>
+  </si>
+  <si>
+    <t>(801) 562-2662</t>
+  </si>
+  <si>
+    <t>10435 2200 W, South Jordan, UT 84095</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Almond+Dental/data=!4m7!3m6!1s0x875288b81d87b9fd:0xf455b7049a575596!8m2!3d40.5617009!4d-111.947938!16s%2Fg%2F1tgh80w6!19sChIJ_bmHHbiIUocRllVXmgS3VfQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:57.882Z</t>
+  </si>
+  <si>
+    <t>B. Kent Bladen, DDS</t>
+  </si>
+  <si>
+    <t>(801) 255-6581</t>
+  </si>
+  <si>
+    <t>1662 9000 S, West Jordan, UT 84088</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/B.+Kent+Bladen,+DDS/data=!4m7!3m6!1s0x875288b87d122c45:0xf1d25d1e5ac1ccea!8m2!3d40.588409!4d-111.9373226!16s%2Fg%2F1vv2sqg2!19sChIJRSwSfbiIUocR6szBWh5d0vE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:06.418Z</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Naisbitt</t>
+  </si>
+  <si>
+    <t>(801) 968-1142</t>
+  </si>
+  <si>
+    <t>5481 W 7800 S #140, West Jordan, UT 84081</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sarah+Naisbitt/data=!4m7!3m6!1s0x87528e41aeef1919:0xf1ad6244e7460d22!8m2!3d40.6092301!4d-112.0202957!16s%2Fg%2F11qgb7zfp0!19sChIJGRnvrkGOUocRIg1G50RirfE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:32.971Z</t>
+  </si>
+  <si>
+    <t>West Jordan UT</t>
+  </si>
+  <si>
+    <t>(801) 568-1710</t>
+  </si>
+  <si>
+    <t>7089 S Redwood Rd, West Jordan, UT 84084</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Jordan+UT/data=!4m7!3m6!1s0x8752893a23f05553:0xe68a7857314803d7!8m2!3d40.622378!4d-111.9372267!16s%2Fg%2F11g0k1xsx4!19sChIJU1XwIzqJUocR1wNIMVd4iuY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:14.198Z</t>
+  </si>
+  <si>
+    <t>The Periodontal Specialists of South Jordan</t>
+  </si>
+  <si>
+    <t>(801) 701-1309</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>10458 S Redwood Rd, South Jordan, UT 84095</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Periodontal+Specialists+of+South+Jordan/data=!4m7!3m6!1s0x875287cf2e5c3017:0x7890371a8a62217c!8m2!3d40.5613452!4d-111.9397138!16s%2Fg%2F11zwmtw4vr!19sChIJFzBcLs-HUocRfCFiiho3kHg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:39:01.863Z</t>
+  </si>
+  <si>
+    <t>North Orem Dental Inc</t>
+  </si>
+  <si>
+    <t>(801) 762-0100</t>
+  </si>
+  <si>
+    <t>1694 N State St, Orem, UT 84057</t>
+  </si>
+  <si>
+    <t>Orem</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Orem+Dental+Inc/data=!4m7!3m6!1s0x874d851c1cc3a48b:0xfc7e9bd3050b18cc!8m2!3d40.328516!4d-111.70863!16s%2Fg%2F1td3rzmt!19sChIJi6TDHByFTYcRzBgLBdObfvw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:39:48.974Z</t>
+  </si>
+  <si>
+    <t>Donald Dodge</t>
+  </si>
+  <si>
+    <t>(801) 225-8060</t>
+  </si>
+  <si>
+    <t>336 W 920 N, Orem, UT 840573042</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Donald+Dodge/data=!4m7!3m6!1s0x874d852f898bffff:0x68281b4303f7d10b!8m2!3d40.3145704!4d-111.7037316!16s%2Fg%2F11sh2c95vb!19sChIJ__-LiS-FTYcRC9H3A0MbKGg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:40:22.046Z</t>
+  </si>
+  <si>
+    <t>Dr. Benjamin R. Frandsen, DDS</t>
+  </si>
+  <si>
+    <t>(801) 375-3355</t>
+  </si>
+  <si>
+    <t>1375 E 800 N #101, Orem, UT 84097</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Benjamin+R.+Frandsen,+DDS/data=!4m7!3m6!1s0x874d90002cb8107f:0xdb1e0054ff35f53e!8m2!3d40.3125953!4d-111.6632385!16s%2Fg%2F1tdx007r!19sChIJfxC4LACQTYcRPvU1_1QAHts?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:03.972Z</t>
+  </si>
+  <si>
+    <t>Dr. Peter N. Smith, DMD</t>
+  </si>
+  <si>
+    <t>(801) 224-0610</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>503 E 770 N, Orem, UT 84097</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Peter+N.+Smith,+DMD/data=!4m7!3m6!1s0x874d854ceeab9cdf:0x12117e5bd87cc330!8m2!3d40.3111526!4d-111.6837265!16s%2Fg%2F1tj33m29!19sChIJ35yr7kyFTYcRMMN82Ft-ERI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:28.960Z</t>
+  </si>
+  <si>
+    <t>Let's Glow Orem</t>
+  </si>
+  <si>
+    <t>(801) 477-0192</t>
+  </si>
+  <si>
+    <t>560 W 800 N Ste 114, Orem, UT 84057</t>
+  </si>
+  <si>
+    <t>Saturday9:30 AM–2:50 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Let%27s+Glow+Orem/data=!4m7!3m6!1s0x874d85801a1a86ed:0x9bb67877602ff777!8m2!3d40.312883!4d-111.709563!16s%2Fg%2F11rkmc1q5q!19sChIJ7YYaGoCFTYcRd_cvYHd4tps?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:42:26.028Z</t>
+  </si>
+  <si>
+    <t>Fresh White Whitening</t>
+  </si>
+  <si>
+    <t>(801) 362-8006</t>
+  </si>
+  <si>
+    <t>1943 N State St, Orem, UT 84057</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fresh+White+Whitening/data=!4m7!3m6!1s0x874d8592fc5d3475:0x51fc315f1673a73!8m2!3d40.3321633!4d-111.7129152!16s%2Fg%2F11s4wj5rkx!19sChIJdTRd_JKFTYcRczpn8RXDHwU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:42:28.803Z</t>
+  </si>
+  <si>
+    <t>Lumina + Co. Teeth Whitening System</t>
+  </si>
+  <si>
+    <t>(801) 500-3880</t>
+  </si>
+  <si>
+    <t>515 W 550 N, Lindon, UT 84042</t>
+  </si>
+  <si>
+    <t>Lindon</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lumina+%2B+Co.+Teeth+Whitening+System/data=!4m7!3m6!1s0x874d83352fab71c3:0x56e60f649f851093!8m2!3d40.3476713!4d-111.7272307!16s%2Fg%2F11h3c4t_0d!19sChIJw3GrLzWDTYcRkxCFn2QP5lY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:42:33.474Z</t>
+  </si>
+  <si>
+    <t>Easton Dental Care</t>
+  </si>
+  <si>
+    <t>(801) 571-3400</t>
+  </si>
+  <si>
+    <t>1434 E 9400 S #206, Sandy, UT 84093</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Easton+Dental+Care/data=!4m7!3m6!1s0x875287fc95a4923d:0xb836fe6cff22f78a!8m2!3d40.5801175!4d-111.8502856!16s%2Fg%2F1hhkxrhjk!19sChIJPZKklfyHUocRivci_2z-Nrg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:39.772Z</t>
+  </si>
+  <si>
+    <t>Dr. Justin J. Woodward, DDS</t>
+  </si>
+  <si>
+    <t>(801) 553-3562</t>
+  </si>
+  <si>
+    <t>9829 S 1300 E Ste 102, Sandy, UT 84092</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Justin+J.+Woodward,+DDS/data=!4m7!3m6!1s0x87527d5937690df9:0x96e2e0b74807cf86!8m2!3d40.5726419!4d-111.8526665!16s%2Fg%2F1v75sczx!19sChIJ-Q1pN1l9UocRhs8HSLfg4pY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:44:16.201Z</t>
+  </si>
+  <si>
+    <t>Dr. Nathan Lewis, DDS</t>
+  </si>
+  <si>
+    <t>(801) 443-4732</t>
+  </si>
+  <si>
+    <t>9730 S 700 E, Sandy, UT 84070</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Nathan+Lewis,+DDS/data=!4m7!3m6!1s0x875287e5ba1e933d:0x2ee598c7eb835385!8m2!3d40.574539!4d-111.8729012!16s%2Fg%2F1ptxqtg82!19sChIJPZMeuuWHUocRhVOD68eY5S4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:45:05.955Z</t>
+  </si>
+  <si>
+    <t>Craig Christensen Dentist</t>
+  </si>
+  <si>
+    <t>(801) 571-5050</t>
+  </si>
+  <si>
+    <t>9455 S Union Square, Sandy, UT 84070</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Craig+Christensen+Dentist/data=!4m7!3m6!1s0x875287e3ca246635:0x274bfd63efa4906a!8m2!3d40.5796067!4d-111.8732356!16s%2Fg%2F1txnpyqr!19sChIJNWYkyuOHUocRapCk72P9Syc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:45:52.256Z</t>
+  </si>
+  <si>
+    <t>Utah Dental Implant &amp; Surgical Center</t>
+  </si>
+  <si>
+    <t>(801) 309-3941</t>
+  </si>
+  <si>
+    <t>1844 E 9400 S, Sandy, UT 84092</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Utah+Dental+Implant+%26+Surgical+Center/data=!4m7!3m6!1s0x87527dab7a675acb:0xd8f536fcace87de3!8m2!3d40.5798488!4d-111.8382822!16s%2Fg%2F11j5syjmgr!19sChIJy1pneqt9UocR433orPw29dg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:56.421Z</t>
+  </si>
+  <si>
+    <t>Cottonwood Heights Dentistry</t>
+  </si>
+  <si>
+    <t>(385) 363-3642</t>
+  </si>
+  <si>
+    <t>2114 Fort Union Blvd, Cottonwood Heights, UT 84121</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cottonwood+Heights+Dentistry/data=!4m7!3m6!1s0x875262f372f9631b:0x6cc659ea302bd756!8m2!3d40.6236032!4d-111.8306228!16s%2Fg%2F1hc3dqhx8!19sChIJG2P5cvNiUocRVtcrMOpZxmw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:47:24.756Z</t>
+  </si>
+  <si>
+    <t>Gregory Randall</t>
+  </si>
+  <si>
+    <t>(801) 727-2626</t>
+  </si>
+  <si>
+    <t>9141 Village Shop Dr, Sandy, UT 84094</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gregory+Randall/data=!4m7!3m6!1s0x875287fe25555555:0xdd1bacb7e01f9cd1!8m2!3d40.5855685!4d-111.8625988!16s%2Fg%2F11rkj81k7t!19sChIJVVVVJf6HUocR0Zwf4LesG90?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:47:33.492Z</t>
+  </si>
+  <si>
+    <t>Dr. Julie M. Buchanan, DDS</t>
+  </si>
+  <si>
+    <t>(435) 628-6168</t>
+  </si>
+  <si>
+    <t>sandale terrace, 382 S Bluff St Ste 200, St. George, UT 84770</t>
+  </si>
+  <si>
+    <t>St. George</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Julie+M.+Buchanan,+DDS/data=!4m7!3m6!1s0x80ca44deabee0cc1:0x167d22494f2517ac!8m2!3d37.1017523!4d-113.5908147!16s%2Fg%2F1tdz9q3b!19sChIJwQzuq95EyoARrBclT0kifRY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:24.662Z</t>
+  </si>
+  <si>
+    <t>Dr. Marden K. Leavitt, DMD</t>
+  </si>
+  <si>
+    <t>(435) 673-6831</t>
+  </si>
+  <si>
+    <t>111 E 100 S, St. George, UT 84770</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Marden+K.+Leavitt,+DMD/data=!4m7!3m6!1s0x80ca44d1a5165f55:0xacf2d6fa98ace5f4!8m2!3d37.1067193!4d-113.5809273!16s%2Fg%2F1td7zcbp!19sChIJVV8WpdFEyoAR9OWsmPrW8qw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:21.344Z</t>
+  </si>
+  <si>
+    <t>Dr. Tyson Jessop ("Dr. T")</t>
+  </si>
+  <si>
+    <t>(435) 628-0511</t>
+  </si>
+  <si>
+    <t>826 S 3000 E, St. George, UT 84790</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tyson+Jessop+%28%22Dr.+T%22%29/data=!4m7!3m6!1s0x80ca5b1286720b05:0xa43a363421b58cde!8m2!3d37.094191!4d-113.523262!16s%2Fg%2F11mk_6vl5c!19sChIJBQtyhhJbyoAR3oy1ITQ2OqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:47.637Z</t>
+  </si>
+  <si>
+    <t>Tyler Torres</t>
+  </si>
+  <si>
+    <t>(435) 688-8827</t>
+  </si>
+  <si>
+    <t>368 E Riverside Dr #6, St. George, UT 84790</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Tyler+Torres/data=!4m7!3m6!1s0x80ca4534ea78d6d9:0xf4615d2df9f5fc8a!8m2!3d37.0830791!4d-113.5743485!16s%2Fg%2F11rwxfbnxb!19sChIJ2dZ46jRFyoARivz1-S1dYfQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:50.642Z</t>
+  </si>
+  <si>
+    <t>Dr. T. Jay Robinson</t>
+  </si>
+  <si>
+    <t>(435) 673-3490</t>
+  </si>
+  <si>
+    <t>446 S Mall Dr, St. George, UT 84790</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+T.+Jay+Robinson/data=!4m7!3m6!1s0x80ca5ae4e69aaaab:0x5f83fe8037b39bcb!8m2!3d37.0999903!4d-113.5389504!16s%2Fg%2F11k3pxj5bb!19sChIJq6qa5uRayoARy5uzN4D-g18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:55.731Z</t>
+  </si>
+  <si>
+    <t>Dr. Bradley Simister</t>
+  </si>
+  <si>
+    <t>(435) 656-3346</t>
+  </si>
+  <si>
+    <t>1054 E Riverside Dr Ste 101, St. George, UT 84790</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Bradley+Simister/data=!4m7!3m6!1s0x80ca5ac5f92ba0bb:0x718e202fcd49f403!8m2!3d37.0877082!4d-113.5607437!16s%2Fg%2F11p07bcvx9!19sChIJu6Ar-cVayoARA_RJzS8gjnE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:52:10.897Z</t>
+  </si>
+  <si>
+    <t>Open Wide Professional Teeth Whitening &amp; Full Body Waxing</t>
+  </si>
+  <si>
+    <t>(435) 680-0517</t>
+  </si>
+  <si>
+    <t>67 E St George Blvd, St. George, UT 84770</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Open+Wide+Professional+Teeth+Whitening+%26+Full+Body+Waxing/data=!4m7!3m6!1s0x80ca453ea7f43143:0xa041f6e2413f77a7!8m2!3d37.1100961!4d-113.5820393!16s%2Fg%2F11td41hxyx!19sChIJQzH0pz5FyoARp3c_QeL2QaA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:42.698Z</t>
+  </si>
+  <si>
+    <t>Beauty by Cilla Esthetics</t>
+  </si>
+  <si>
+    <t>(435) 862-1084</t>
+  </si>
+  <si>
+    <t>Skin care clinic</t>
+  </si>
+  <si>
+    <t>192 E 200 N Ste 201, St. George, UT 84770</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Beauty+by+Cilla+Esthetics/data=!4m7!3m6!1s0x80ca45be6da53fe5:0x3fcd626b13518bd0!8m2!3d37.1114201!4d-113.5794214!16s%2Fg%2F11y3mb180c!19sChIJ5T-lbb5FyoAR0ItRE2tizT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:51.186Z</t>
+  </si>
+  <si>
+    <t>Donald Echols</t>
+  </si>
+  <si>
+    <t>(435) 652-1605</t>
+  </si>
+  <si>
+    <t>754 S Main St #7, St. George, UT 84770</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Donald+Echols/data=!4m7!3m6!1s0x80ca4528713fffff:0x152efc3c6e78c0f4!8m2!3d37.0959823!4d-113.5842891!16s%2Fg%2F11jz9jf1dx!19sChIJ__8_cShFyoAR9MB4bjz8LhU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:54:10.949Z</t>
+  </si>
+  <si>
+    <t>Burdett Dental PC</t>
+  </si>
+  <si>
+    <t>(801) 475-0680</t>
+  </si>
+  <si>
+    <t>5331 S 500 E Suite C, Ogden, UT 84405</t>
+  </si>
+  <si>
+    <t>Ogden</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Burdett+Dental+PC/data=!4m7!3m6!1s0x875305903c6793fb:0x5f0cce72a8a21a91!8m2!3d41.1666633!4d-111.9689712!16s%2Fg%2F1v9gvyyh!19sChIJ-5NnPJAFU4cRkRqiqHLODF8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:12.283Z</t>
+  </si>
+  <si>
+    <t>Dr. Joseph Hale</t>
+  </si>
+  <si>
+    <t>(801) 334-9444</t>
+  </si>
+  <si>
+    <t>3500 Harrison Blvd, Ogden, UT 84403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joseph+Hale/data=!4m7!3m6!1s0x875308b470e55555:0xd438a99f1d5bae0c!8m2!3d41.1991774!4d-111.9483832!16s%2Fg%2F11p07bghtn!19sChIJVVXlcLQIU4cRDK5bHZ-pONQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:12.700Z</t>
+  </si>
+  <si>
+    <t>Mark C. Geddes DDS</t>
+  </si>
+  <si>
+    <t>(888) 718-5960</t>
+  </si>
+  <si>
+    <t>1220 33rd St B, Ogden, UT 84403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mark+C.+Geddes+DDS/data=!4m7!3m6!1s0x8753093318887b4f:0xb441ae09bc9597c3!8m2!3d41.2035074!4d-111.9478798!16s%2Fg%2F11jp4rsy74!19sChIJT3uIGDMJU4cRw5eVvAmuQbQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:15.446Z</t>
+  </si>
+  <si>
+    <t>Malan Family Dentistry</t>
+  </si>
+  <si>
+    <t>(801) 627-0410</t>
+  </si>
+  <si>
+    <t>3860 Jackson Ave Ste 4, Ogden, UT 84403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Malan+Family+Dentistry/data=!4m7!3m6!1s0x87530f529e94987b:0x974306999ae0803a!8m2!3d41.1928633!4d-111.9540955!16s%2Fg%2F1tlgyf8n!19sChIJe5iUnlIPU4cROoDgmpkGQ5c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:35.320Z</t>
+  </si>
+  <si>
+    <t>Odontólogo esteticista dental</t>
+  </si>
+  <si>
+    <t>(385) 294-8441</t>
+  </si>
+  <si>
+    <t>Cosmetic dentist</t>
+  </si>
+  <si>
+    <t>2433 Adams Ave #238, Ogden, UT 84401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Odont%C3%B3logo+esteticista+dental/data=!4m7!3m6!1s0x87530f11cf466fb9:0x365e517e0d79e025!8m2!3d41.2220714!4d-111.9682284!16s%2Fg%2F11yqpt6cjw!19sChIJuW9GzxEPU4cRJeB5DX5RXjY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:38.250Z</t>
+  </si>
+  <si>
+    <t>Dr. Mathew Schweppe</t>
+  </si>
+  <si>
+    <t>(801) 479-9220</t>
+  </si>
+  <si>
+    <t>2850 N 2000 W #205, Ogden, UT 84404</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mathew+Schweppe/data=!4m7!3m6!1s0x87530d46e71210ad:0xecbc4bb4b7d172ae!8m2!3d41.3087342!4d-112.0272794!16s%2Fg%2F11p079_wnj!19sChIJrRAS50YNU4cRrnLRt7RLvOw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:56.105Z</t>
+  </si>
+  <si>
+    <t>Allred and Oliverson Orthodontics</t>
+  </si>
+  <si>
+    <t>(801) 393-6200</t>
+  </si>
+  <si>
+    <t>3550 Harrison Blvd, Ogden, UT 84403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Allred+and+Oliverson+Orthodontics/data=!4m7!3m6!1s0x875308b3885bf9a1:0x71e0c75d3930fb2b!8m2!3d41.1986532!4d-111.9483832!16s%2Fg%2F11c2mcppp9!19sChIJoflbiLMIU4cRK_swOV3H4HE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:12.643Z</t>
+  </si>
+  <si>
+    <t>Utah Orthodontics</t>
+  </si>
+  <si>
+    <t>(801) 394-4415</t>
+  </si>
+  <si>
+    <t>1220 33rd St A, Ogden, UT 84403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Utah+Orthodontics/data=!4m7!3m6!1s0x875309cec031a54b:0xd55d90cd467c533f!8m2!3d41.2034825!4d-111.9478243!16s%2Fg%2F11fkbwlkym!19sChIJS6UxwM4JU4cRP1N8Rs2QXdU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:15.462Z</t>
+  </si>
+  <si>
+    <t>Lakeside Orthodontics</t>
+  </si>
+  <si>
+    <t>(801) 621-5892</t>
+  </si>
+  <si>
+    <t>1067 24th St, Ogden, UT 84401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lakeside+Orthodontics/data=!4m7!3m6!1s0x8753095b080b12ab:0xefebc4d641ecbe95!8m2!3d41.222293!4d-111.951747!16s%2Fg%2F11tgdbvzcs!19sChIJqxILCFsJU4cRlb7sQdbE6-8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:18.572Z</t>
+  </si>
+  <si>
+    <t>Boyd L Jacobson PC</t>
+  </si>
+  <si>
+    <t>(801) 479-7069</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>1508 E Skyline Dr #100, South Ogden, UT 84405</t>
+  </si>
+  <si>
+    <t>South Ogden</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Boyd+L+Jacobson+PC/data=!4m7!3m6!1s0x8753067cb2a0970f:0xb3c339010c700ddc!8m2!3d41.1518004!4d-111.9406515!16s%2Fg%2F1tfc72hd!19sChIJD5egsnwGU4cR3A1wDAE5w7M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:23.565Z</t>
+  </si>
+  <si>
+    <t>Dr. Gary Hoopes</t>
+  </si>
+  <si>
+    <t>(801) 399-5220</t>
+  </si>
+  <si>
+    <t>333 2nd St Ste 1A, Ogden, UT 84404</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gary+Hoopes/data=!4m7!3m6!1s0x87530c1e675aaaab:0x9b9cacea07166888!8m2!3d41.2584564!4d-111.9715785!16s%2Fg%2F11p079zxzp!19sChIJq6paZx4MU4cRiGgWB-qsnJs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:55.215Z</t>
   </si>
 </sst>
 </file>
@@ -553,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -816,6 +2046,2999 @@
         <v>53</v>
       </c>
     </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>92</v>
+      </c>
+      <c r="M13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>117</v>
+      </c>
+      <c r="M17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>116</v>
+      </c>
+      <c r="J18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>122</v>
+      </c>
+      <c r="M18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>135</v>
+      </c>
+      <c r="M20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>151</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>152</v>
+      </c>
+      <c r="M23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>157</v>
+      </c>
+      <c r="M24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>164</v>
+      </c>
+      <c r="M25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>170</v>
+      </c>
+      <c r="M26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>175</v>
+      </c>
+      <c r="M27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" t="s">
+        <v>182</v>
+      </c>
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>183</v>
+      </c>
+      <c r="M28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>188</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>189</v>
+      </c>
+      <c r="M29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" t="s">
+        <v>116</v>
+      </c>
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>194</v>
+      </c>
+      <c r="M30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>199</v>
+      </c>
+      <c r="M31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>206</v>
+      </c>
+      <c r="M32" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" t="s">
+        <v>205</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>211</v>
+      </c>
+      <c r="M33" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>213</v>
+      </c>
+      <c r="B34" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>216</v>
+      </c>
+      <c r="M34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" t="s">
+        <v>205</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>29</v>
+      </c>
+      <c r="I35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s">
+        <v>221</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>222</v>
+      </c>
+      <c r="M35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" t="s">
+        <v>232</v>
+      </c>
+      <c r="E37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" t="s">
+        <v>116</v>
+      </c>
+      <c r="J37" t="s">
+        <v>233</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>234</v>
+      </c>
+      <c r="M37" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" t="s">
+        <v>239</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>240</v>
+      </c>
+      <c r="M38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" t="s">
+        <v>244</v>
+      </c>
+      <c r="E39" t="s">
+        <v>239</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>75</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>245</v>
+      </c>
+      <c r="M39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" t="s">
+        <v>239</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>250</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>251</v>
+      </c>
+      <c r="M40" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" t="s">
+        <v>239</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>98</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>256</v>
+      </c>
+      <c r="M41" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>261</v>
+      </c>
+      <c r="M42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B43" t="s">
+        <v>264</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>265</v>
+      </c>
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>45</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>266</v>
+      </c>
+      <c r="M43" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>268</v>
+      </c>
+      <c r="B44" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>270</v>
+      </c>
+      <c r="E44" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" t="s">
+        <v>116</v>
+      </c>
+      <c r="J44" t="s">
+        <v>45</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>271</v>
+      </c>
+      <c r="M44" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45" t="s">
+        <v>239</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" t="s">
+        <v>116</v>
+      </c>
+      <c r="J45" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>277</v>
+      </c>
+      <c r="M45" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>279</v>
+      </c>
+      <c r="B46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" t="s">
+        <v>281</v>
+      </c>
+      <c r="E46" t="s">
+        <v>282</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" t="s">
+        <v>282</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>45</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>288</v>
+      </c>
+      <c r="M47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>292</v>
+      </c>
+      <c r="E48" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>293</v>
+      </c>
+      <c r="M48" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>295</v>
+      </c>
+      <c r="B49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C49" t="s">
+        <v>297</v>
+      </c>
+      <c r="D49" t="s">
+        <v>298</v>
+      </c>
+      <c r="E49" t="s">
+        <v>282</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>299</v>
+      </c>
+      <c r="I49" t="s">
+        <v>300</v>
+      </c>
+      <c r="J49" t="s">
+        <v>45</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>301</v>
+      </c>
+      <c r="M49" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>303</v>
+      </c>
+      <c r="B50" t="s">
+        <v>304</v>
+      </c>
+      <c r="C50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" t="s">
+        <v>305</v>
+      </c>
+      <c r="E50" t="s">
+        <v>282</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>51</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>306</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>307</v>
+      </c>
+      <c r="M50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>309</v>
+      </c>
+      <c r="B51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C51" t="s">
+        <v>231</v>
+      </c>
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51" t="s">
+        <v>282</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>45</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>312</v>
+      </c>
+      <c r="M51" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>314</v>
+      </c>
+      <c r="B52" t="s">
+        <v>315</v>
+      </c>
+      <c r="C52" t="s">
+        <v>231</v>
+      </c>
+      <c r="D52" t="s">
+        <v>316</v>
+      </c>
+      <c r="E52" t="s">
+        <v>317</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>318</v>
+      </c>
+      <c r="M52" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>320</v>
+      </c>
+      <c r="B53" t="s">
+        <v>321</v>
+      </c>
+      <c r="C53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" t="s">
+        <v>322</v>
+      </c>
+      <c r="E53" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>98</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>323</v>
+      </c>
+      <c r="M53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+      <c r="C54" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54" t="s">
+        <v>327</v>
+      </c>
+      <c r="E54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>45</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>328</v>
+      </c>
+      <c r="M54" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>330</v>
+      </c>
+      <c r="B55" t="s">
+        <v>331</v>
+      </c>
+      <c r="C55" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" t="s">
+        <v>332</v>
+      </c>
+      <c r="E55" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>98</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>333</v>
+      </c>
+      <c r="M55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>151</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>338</v>
+      </c>
+      <c r="M56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" t="s">
+        <v>342</v>
+      </c>
+      <c r="E57" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" t="s">
+        <v>116</v>
+      </c>
+      <c r="J57" t="s">
+        <v>343</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>344</v>
+      </c>
+      <c r="M57" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>346</v>
+      </c>
+      <c r="B58" t="s">
+        <v>347</v>
+      </c>
+      <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" t="s">
+        <v>348</v>
+      </c>
+      <c r="E58" t="s">
+        <v>97</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>163</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>343</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>349</v>
+      </c>
+      <c r="M58" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>351</v>
+      </c>
+      <c r="B59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C59" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59" t="s">
+        <v>353</v>
+      </c>
+      <c r="E59" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>29</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>45</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>354</v>
+      </c>
+      <c r="M59" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>356</v>
+      </c>
+      <c r="B60" t="s">
+        <v>357</v>
+      </c>
+      <c r="C60" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60" t="s">
+        <v>358</v>
+      </c>
+      <c r="E60" t="s">
+        <v>359</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>75</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>360</v>
+      </c>
+      <c r="M60" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+      <c r="C61" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" t="s">
+        <v>364</v>
+      </c>
+      <c r="E61" t="s">
+        <v>359</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>29</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>365</v>
+      </c>
+      <c r="M61" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>367</v>
+      </c>
+      <c r="B62" t="s">
+        <v>368</v>
+      </c>
+      <c r="C62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D62" t="s">
+        <v>369</v>
+      </c>
+      <c r="E62" t="s">
+        <v>359</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>370</v>
+      </c>
+      <c r="M62" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>372</v>
+      </c>
+      <c r="B63" t="s">
+        <v>373</v>
+      </c>
+      <c r="C63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" t="s">
+        <v>374</v>
+      </c>
+      <c r="E63" t="s">
+        <v>359</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>45</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>375</v>
+      </c>
+      <c r="M63" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>377</v>
+      </c>
+      <c r="B64" t="s">
+        <v>378</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" t="s">
+        <v>379</v>
+      </c>
+      <c r="E64" t="s">
+        <v>359</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" t="s">
+        <v>116</v>
+      </c>
+      <c r="J64" t="s">
+        <v>30</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>380</v>
+      </c>
+      <c r="M64" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>382</v>
+      </c>
+      <c r="B65" t="s">
+        <v>383</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" t="s">
+        <v>384</v>
+      </c>
+      <c r="E65" t="s">
+        <v>359</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>45</v>
+      </c>
+      <c r="I65" t="s">
+        <v>116</v>
+      </c>
+      <c r="J65" t="s">
+        <v>45</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>385</v>
+      </c>
+      <c r="M65" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>387</v>
+      </c>
+      <c r="B66" t="s">
+        <v>388</v>
+      </c>
+      <c r="C66" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" t="s">
+        <v>389</v>
+      </c>
+      <c r="E66" t="s">
+        <v>359</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>390</v>
+      </c>
+      <c r="M66" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>392</v>
+      </c>
+      <c r="B67" t="s">
+        <v>393</v>
+      </c>
+      <c r="C67" t="s">
+        <v>394</v>
+      </c>
+      <c r="D67" t="s">
+        <v>395</v>
+      </c>
+      <c r="E67" t="s">
+        <v>359</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>396</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>397</v>
+      </c>
+      <c r="M67" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>399</v>
+      </c>
+      <c r="B68" t="s">
+        <v>400</v>
+      </c>
+      <c r="C68" t="s">
+        <v>275</v>
+      </c>
+      <c r="D68" t="s">
+        <v>401</v>
+      </c>
+      <c r="E68" t="s">
+        <v>359</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>29</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>45</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>402</v>
+      </c>
+      <c r="M68" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>404</v>
+      </c>
+      <c r="B69" t="s">
+        <v>405</v>
+      </c>
+      <c r="C69" t="s">
+        <v>43</v>
+      </c>
+      <c r="D69" t="s">
+        <v>406</v>
+      </c>
+      <c r="E69" t="s">
+        <v>407</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>30</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>408</v>
+      </c>
+      <c r="M69" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>410</v>
+      </c>
+      <c r="B70" t="s">
+        <v>411</v>
+      </c>
+      <c r="C70" t="s">
+        <v>43</v>
+      </c>
+      <c r="D70" t="s">
+        <v>412</v>
+      </c>
+      <c r="E70" t="s">
+        <v>407</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>45</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>413</v>
+      </c>
+      <c r="M70" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" t="s">
+        <v>416</v>
+      </c>
+      <c r="C71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" t="s">
+        <v>417</v>
+      </c>
+      <c r="E71" t="s">
+        <v>407</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>181</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>45</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>418</v>
+      </c>
+      <c r="M71" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>420</v>
+      </c>
+      <c r="B72" t="s">
+        <v>421</v>
+      </c>
+      <c r="C72" t="s">
+        <v>43</v>
+      </c>
+      <c r="D72" t="s">
+        <v>422</v>
+      </c>
+      <c r="E72" t="s">
+        <v>407</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>59</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>30</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>423</v>
+      </c>
+      <c r="M72" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>425</v>
+      </c>
+      <c r="B73" t="s">
+        <v>426</v>
+      </c>
+      <c r="C73" t="s">
+        <v>427</v>
+      </c>
+      <c r="D73" t="s">
+        <v>428</v>
+      </c>
+      <c r="E73" t="s">
+        <v>407</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>45</v>
+      </c>
+      <c r="I73" t="s">
+        <v>116</v>
+      </c>
+      <c r="J73" t="s">
+        <v>22</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>429</v>
+      </c>
+      <c r="M73" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>431</v>
+      </c>
+      <c r="B74" t="s">
+        <v>432</v>
+      </c>
+      <c r="C74" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" t="s">
+        <v>407</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>45</v>
+      </c>
+      <c r="I74" t="s">
+        <v>116</v>
+      </c>
+      <c r="J74" t="s">
+        <v>45</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>434</v>
+      </c>
+      <c r="M74" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>436</v>
+      </c>
+      <c r="B75" t="s">
+        <v>437</v>
+      </c>
+      <c r="C75" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" t="s">
+        <v>438</v>
+      </c>
+      <c r="E75" t="s">
+        <v>407</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>439</v>
+      </c>
+      <c r="M75" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>441</v>
+      </c>
+      <c r="B76" t="s">
+        <v>442</v>
+      </c>
+      <c r="C76" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76" t="s">
+        <v>443</v>
+      </c>
+      <c r="E76" t="s">
+        <v>407</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>30</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>444</v>
+      </c>
+      <c r="M76" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>446</v>
+      </c>
+      <c r="B77" t="s">
+        <v>447</v>
+      </c>
+      <c r="C77" t="s">
+        <v>108</v>
+      </c>
+      <c r="D77" t="s">
+        <v>448</v>
+      </c>
+      <c r="E77" t="s">
+        <v>407</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>29</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>30</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>449</v>
+      </c>
+      <c r="M77" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>451</v>
+      </c>
+      <c r="B78" t="s">
+        <v>452</v>
+      </c>
+      <c r="C78" t="s">
+        <v>453</v>
+      </c>
+      <c r="D78" t="s">
+        <v>454</v>
+      </c>
+      <c r="E78" t="s">
+        <v>455</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>456</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>45</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>457</v>
+      </c>
+      <c r="M78" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>459</v>
+      </c>
+      <c r="B79" t="s">
+        <v>460</v>
+      </c>
+      <c r="C79" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" t="s">
+        <v>461</v>
+      </c>
+      <c r="E79" t="s">
+        <v>407</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>29</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>45</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>462</v>
+      </c>
+      <c r="M79" t="s">
+        <v>463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
